--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,6 +1053,721 @@
         <v>250</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8419.888723686912</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3358.181542652014</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1721.033640636922</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3529655897131331</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.1069957690918462</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>91595.24883734586</v>
+      </c>
+      <c r="L13" t="n">
+        <v>35393.4596668983</v>
+      </c>
+      <c r="M13" t="n">
+        <v>17983.54651994562</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.3530555981988385</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.1070204232376203</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.06669014812811887</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.03215618428828618</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.04219401103942534</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.02321336167659763</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.01829588965735189</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.006100920594155682</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.001994843106469135</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.002708739133683608</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.007441929839803268</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.001868895663175856</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.002396562552236689</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.000869991606806587</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.001293229828996</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.000196175569972546</v>
+      </c>
+      <c r="O16" t="n">
+        <v>6.877736976328098e-05</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>100</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0006839520248654686</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0002980483770361113</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.0009224959749470325</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.0001008269804128768</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.216439627682969e-05</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>100</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.715656324817084e-05</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3.545128190994177e-05</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6.490039259445615e-05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>7.383441551275677e-05</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.381420379563165e-05</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>100</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.001709107392741635</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0007871941604960717</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.001806691995564976</v>
+      </c>
+      <c r="N19" t="n">
+        <v>5.275281041704515e-05</v>
+      </c>
+      <c r="O19" t="n">
+        <v>6.835530267976926e-05</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>100</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.954739724467853e-05</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8.733602810767101e-06</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4.693386073555791e-05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.396993990816048e-05</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.086094230167679e-05</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>100</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>100</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.0001979847393430005</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5.83843302566905e-05</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0002395304821855847</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.0002225692249031216</v>
+      </c>
+      <c r="O21" t="n">
+        <v>6.232449481073183e-05</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>100</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0002722482020996734</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.000138055458629253</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.001237965987567097</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8.507780626719103e-05</v>
+      </c>
+      <c r="O22" t="n">
+        <v>6.856007228381102e-05</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>100</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>9.226901426149393e-05</v>
+      </c>
+      <c r="L23" t="n">
+        <v>5.506458677058522e-05</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.0008248771822099201</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.0001969519414107906</v>
+      </c>
+      <c r="O23" t="n">
+        <v>6.391074933421281e-05</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>100</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100</v>
+      </c>
+      <c r="C24" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.002131879883319278</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.000384381860982775</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.1769644321235926</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.05951836497467748</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.003970088319675757</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1771,4 +1772,765 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0001588723366264804</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.955694519852906e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>9.255529047333503e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0001007596589735602</v>
+      </c>
+      <c r="O2" t="n">
+        <v>8.501256095919924e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7.524625933053565e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.940100031879818e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0001579627016650867</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.000200644635402502</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4.599024262404709e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0005832018431451263</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0002083758021114794</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0003359447926225567</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0001745846391796704</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0001060656178571023</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0002387646133750558</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7.368717429133281e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0004186569854044646</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0001021150214978653</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.947897777052429e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.73859435266548e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.173727424780689e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5.592754371464555e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0001255764155244461</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.673914861859592e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0004398196456428888</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001826901987936624</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0003856518023857439</v>
+      </c>
+      <c r="N7" t="n">
+        <v>7.223985573672356e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.831949593882513e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.01687657441752211</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.004710715276797597</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.01074830093172584</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0001394899203699174</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.060228206822531e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.715656324817084e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.545128190994177e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6.490039259445615e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7.383441551275677e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.381420379563165e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001084097712653935</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.253936230053637e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8.923118287964924e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.053296859932593e-05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.879052354440722e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0005617600463561045</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0002568293787368754</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0005266055187112418</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5.827434555059964e-05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4.680066746193088e-05</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0006334799268205215</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0002740653137748037</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0004452960379287802</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0001106085670762809</v>
+      </c>
+      <c r="O12" t="n">
+        <v>9.600560366973257e-05</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.00015589279774105</v>
+      </c>
+      <c r="L13" t="n">
+        <v>7.425231052149436e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0001105503474174624</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0003155509266469263</v>
+      </c>
+      <c r="O13" t="n">
+        <v>9.345067001417566e-05</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2533,4 +2534,545 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9.532054815328558e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5.200291380429977e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.000114828779789014</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.497626400980323e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.959317812244473e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0001716929593275044</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7.143897298276051e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0002233668526963895</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6.84805128720178e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.097880118537332e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0002231882813377093</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9.936222635683006e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0002864527698471759</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.163155621657813e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.004339426800663e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0001653913378787869</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7.851277367335835e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0002632934049928114</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.629204985167375e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.228555085524286e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9.234591595959077e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.380309007593051e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0001019719981455006</v>
+      </c>
+      <c r="N6" t="n">
+        <v>9.098306977928544e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.362816857480754e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.715656324817084e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.545128190994177e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6.490039259445615e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>7.383441551275677e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.381420379563165e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.696675197584925e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.749387123649341e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6.176341009424908e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>6.317606066180862e-05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.378831792958328e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001779200568977974</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6.90288945464366e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.000183332576480773</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0002962799401652276</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5.35210251524021e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3075,4 +3076,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7.251938608863344e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3.062114829162203e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8.270602358756145e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.051978679766217e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.885230985543677e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.175511823326759e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.357430341695112e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5.407821848422731e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.144899461169721e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.555134540132849e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001347164450518011</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4.557480748564751e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7.753505129604106e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.999633308260427e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.53289819451486e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.576649563925728e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.557174635553834e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.203876339447883e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.275576154936377e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.5040078294028e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0007864485349609987</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0002880423631947433</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0008029337694509385</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.002477602804815e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.883140004602646e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0003458694707821371</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001368935301555861</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0004033169889974668</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5.218787388987913e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.382762927255213e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9.747813389768733e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4.679444204862066e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.00015891464029806</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7.063550121523158e-05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.225577608484045e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.715656324817084e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.545128190994177e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6.490039259445615e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7.383441551275677e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.381420379563165e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.186215556067998e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3.885882500718148e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5.22004892261004e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7.659942682408645e-05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.517667666423731e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.425380454192747e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.001014837070976e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5.555453314864528e-05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7.695886955666179e-05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.535482544096083e-05</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>6.703858655430612e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4.201559732133393e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>6.272173339764577e-05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7.72491430449096e-05</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.549864926115431e-05</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.785972697244692e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.252165770824137e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6.463476929440096e-05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7.728509143911335e-05</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.551672100174021e-05</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6.864087090392091e-05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4.303968367330741e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6.654282163974252e-05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>7.731413389080468e-05</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.553118478142335e-05</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvector Angle" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3892,4 +3893,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.130667259363674e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3.887966104001186e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>6.614777951723113e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>7.383408845084578e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.384967226426097e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.001720224968876564</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0003179183182809605</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0006209594131217998</v>
+      </c>
+      <c r="N3" t="n">
+        <v>7.043717954077091e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.689717793978528e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0005417219518792098</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6.141792520785427e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>6.939276206511631e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5.334551277103854e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.601461722805436e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.006094782283370255</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0006707610502839327</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.001255514845081034</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7.043118899285173e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.689925209108571e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.715656324817084e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.545128190994177e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6.490039259445615e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7.383441551275677e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.381420379563165e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0007712595063353676</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001150919202076069</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0002152930134237532</v>
+      </c>
+      <c r="N7" t="n">
+        <v>7.043711351814709e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.691648092201794e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0006806282179525424</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0001165598060992441</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0001714814048927924</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5.334561791057909e-05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.60207049393559e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001582698997505109</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.343705228856499e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4.856846426181302e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7.043716923460584e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.69234619460755e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.130794600876796e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3.888015468440121e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6.615057748826211e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7.383408882327229e-05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.384967195687906e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246FC0B4-34F0-4646-8D8A-78B13D8974A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,20 @@
     <sheet name="Eigenvalue Ratio" sheetId="4" r:id="rId5"/>
     <sheet name="Eigenvector Angle" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 

--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dc858\Documents\Projects\RBF-FD-Elliptic\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246FC0B4-34F0-4646-8D8A-78B13D8974A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8BC40E-0DC8-4CFD-9FA0-643FF31F8875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,4 +1057,930 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1664854602060465</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0593186896187588</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.08750333871920063</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.1683105329375875</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.03885360161011485</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.1657266632502236</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.05903031463804649</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0871145198004836</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.1683348689477839</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.03886644273163496</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.009153456819652196</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.00608920417897185</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.009243114731596733</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.009314855475981796</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.005798216953550803</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.00702961396887428</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.004743058081748714</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.007893671166564677</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.008875774737474154</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.004907090842964975</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0003225249229620972</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.000111017178862803</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0002920043534352647</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0005258322259099803</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0001215515895535778</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0002286656176599509</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7.253158055177629e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.000189888879952308</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0005415613027537915</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.000129209119662398</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.055597915897754e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.340730404532689e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>8.591752269680814e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0003580752408651098</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0001121572495164942</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0006822871441467448</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0002731403927547455</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0008475628716684338</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0003636600746068398</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9.369800946194555e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.361082471921287e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.108114242402136e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.483705934578053e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0001152346947304556</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.905545641799866e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.683421035437217e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.488688863735333e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0001322535437346697</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0002955903171802797</v>
+      </c>
+      <c r="O11" t="n">
+        <v>8.698964442081736e-05</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.311513843800276e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>9.517185127694567e-06</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0005919646071415696</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.00253872111005417</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0006642099669280709</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.149276085315983e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.957435279054722e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.001950762088699405</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.01707874765880804</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.002482681410451853</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.000536716658424701</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0004357174929485001</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.001091903132465252</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.07745222047600676</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.01477068717199525</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.005849997795172481</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.005195223403518706</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.005876541242889564</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2103368880751618</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.04732687145102096</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>30</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.1593678190011436</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1464708837645474</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1403433757398201</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.8588568115241542</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.2355066295811421</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1983,4 +1984,875 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1785530565489405</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.01769783083842199</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.05968551600056385</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0001585471515622067</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0001366939076852924</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8.923297741259418e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.13393433807526e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.000164997778231207</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0001575042420733342</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4.716537756458208e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001042685489666307</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4.978972850486495e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0001468139647795028</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8.291639806990979e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.706813287400291e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.905337141433888e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3.430865138098574e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0002243058568923152</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.959294561643157e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.644938890162426e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0001655711079118207</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9.548548004545891e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0001729687951107113</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8.369895022536532e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>7.290436006742063e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0004403956590008497</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001903250293804904</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0003801574496853431</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9.781338508903722e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>9.620930805271565e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.001027394404964703</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.000419512242428396</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.001364568434885891</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0001059653284863005</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.000113079871241762</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8.333360505653543e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.880339246268362e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0002315208409884614</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.000112963262687937</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.821370887300927e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7.103372791478002e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.68146340750161e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8.916987251700264e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>9.748482222349874e-05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.604132190032485e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.963551814771347e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.269059883093448e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5.622911979146538e-05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0001219517261262385</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4.164130002998475e-05</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0002883507296025164</v>
+      </c>
+      <c r="L12" t="n">
+        <v>7.741161179453353e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0001380150462845586</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.000266513346506866</v>
+      </c>
+      <c r="O12" t="n">
+        <v>8.470208426065527e-05</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>175</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8.578889548885795e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.433322169679516e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6.703081837998725e-05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5.026952703382065e-05</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.683766729105044e-05</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0001058220551727615</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3.564036118268749e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5.873892976714899e-05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.657844533524258e-05</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.638313253148118e-05</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>250</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0001420078079246596</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4.589491319629712e-05</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6.672284604492622e-05</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.068277871461987e-05</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.811345117101635e-05</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2855,4 +2856,655 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.461665621014362e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.25663362500034e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.983757788513124e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>7.200256682565929e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.877815263481837e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.486108722771638e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.25588439654976e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.009086508296899e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>7.662278330689394e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.975837907704327e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.508125054695755e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.265781516854079e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.153458630151018e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>7.972325143579977e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.036427068548075e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.506274404943044e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.257727353037729e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.063709312370806e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>8.112988956041596e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.075387563158378e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.530491582291891e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.268533120655258e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.228218777615083e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8.179665356256838e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.090429182370517e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.459671842700315e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.174454945862697e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.113100726548775e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0001134347281841542</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.808170599398016e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.435015524413351e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.165038231017454e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.069931114028587e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0001145219929587552</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.832265878517685e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.361082471921287e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.108114242402136e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.483705934578053e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0001152346947304556</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.905545641799866e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001115713425496485</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3.151125361804579e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0002078334809042067</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0001267356688266236</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.14287304208646e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0001919595061915836</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.01837174159024e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0001925322049680285</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0004072820280243158</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4.239779224012116e-05</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3507,4 +3508,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.384141246100084e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.015456215761651e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.740769839327224e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>7.910036677368966e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.962787799477297e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.311834685044111e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9.481596907845235e-06</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.580637081628814e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6.331345615844409e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.718067531811667e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.513429096500482e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8.631691891830906e-06</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.363141937276089e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.599373041534269e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.568984427564253e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.793174627878471e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.193678737875087e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6.645118553475946e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.526910604727326e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.584520754927541e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0005984369127461989</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0002262646092460992</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.002537446909294367</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7.735078025050812e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.965151935484029e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.496465870792622e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.142626923941045e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.464361707094119e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9.180083606024383e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.283451586411513e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.076973216479566e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.328662889507054e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5.794095307793753e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0001117805595501738</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.808097513243979e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.361082471921287e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.108114242402136e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.483705934578053e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0001152346947304556</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.905545641799866e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.227000282934915e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.835784303799532e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8.484822997129987e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0001182179509115181</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.990932129406878e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.561839830192981e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.706991989242749e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6.997925671533176e-05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0001186057797942234</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.002110415207571e-05</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.07157649574047e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.630813260029033e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>6.18749741559386e-05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.000119071675176462</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.011137359470768e-05</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.020145152332381e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.625281659323037e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6.129279955962675e-05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.000119133542754344</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.012270957362733e-05</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.980221755857487e-05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.621540891069371e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6.08950200867866e-05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.0001191830503036641</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.01317885352406e-05</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Eigenvector Angle" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4324,4 +4325,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.44986003884065e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.414009441838943e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7.436414610758647e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0001183764892243101</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.893693696014334e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.663117693468906e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.32348820173375e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4.232569781725632e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.313315310743768e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.396383897975848e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.87556486309456e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.235388288850638e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.303176776416993e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.718514946881359e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.383892441374085e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.861322841238263e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.343535326845032e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.186104906833719e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.178199476981794e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.394608113330317e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.361082471921287e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.108114242402136e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.483705934578053e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0001152346947304556</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.905545641799866e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.49422664221758e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.316917831045835e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.654922651094687e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5.185679531981044e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.403828065973646e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.771536545363179e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.259810430972837e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.023815850322971e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.718525920823571e-05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.392455293945891e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.962214164368955e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.375476843436055e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.380210921166938e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.218743260645061e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.402896908129364e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.4498677034352e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.414011781118043e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7.436450864783305e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0001183764929655635</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.893693720844198e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1055,6 +1055,556 @@
         </is>
       </c>
       <c r="Q11" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.02594876959666952</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.02377641650003685</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.02304471521269408</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.01527582278171621</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.01881107421491665</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>30</v>
+      </c>
+      <c r="B13" t="n">
+        <v>30</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.01197032347692574</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.01095919782513719</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.01061512878929426</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.007022495701824443</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.008760683024118213</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>50</v>
+      </c>
+      <c r="B14" t="n">
+        <v>50</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.004440605209351252</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.004057804328488757</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.003928317885334275</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.002606939439180846</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.00326217299343161</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>75</v>
+      </c>
+      <c r="B15" t="n">
+        <v>75</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.002005535662171063</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.001828477500031621</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.001769843023134046</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.001174392216765028</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.001472667607612331</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.001135793695212327</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.00103555656359563</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.001002293378963933</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.0006657024949418853</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.0008345913375595516</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125</v>
+      </c>
+      <c r="B17" t="n">
+        <v>125</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0007294574848049906</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.000665460086012631</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.0006440702528063183</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.0004278534124795499</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.0005364819308334207</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>150</v>
+      </c>
+      <c r="B18" t="n">
+        <v>150</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.0005076546620867402</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.0004633771112647862</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.0004484774063693989</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.0002980135472181496</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.0003736287930199195</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>175</v>
+      </c>
+      <c r="B19" t="n">
+        <v>175</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.0003737320605345014</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0003410985810881198</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.0003301283055711963</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.0002193596216003755</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.0002750611468202974</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>200</v>
+      </c>
+      <c r="B20" t="n">
+        <v>200</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.0002865639041114003</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.0002615269727248047</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.0002531146572442974</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.0001682299328012132</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.000210909524496917</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>250</v>
+      </c>
+      <c r="B21" t="n">
+        <v>250</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.0001837550490671772</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.0001677131140571448</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0001623174953925637</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.0001078894553904069</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0001352639552030778</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
         <v>250</v>
       </c>
     </row>

--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -1619,7 +1619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2531,6 +2531,831 @@
         </is>
       </c>
       <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>500</v>
+      </c>
+      <c r="B17" t="n">
+        <v>500</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4212.326877272338</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2795.779531038314</v>
+      </c>
+      <c r="M17" t="n">
+        <v>5942.355564831777</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.9997205575778536</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.9997205824732387</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>500</v>
+      </c>
+      <c r="B18" t="n">
+        <v>500</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1052.19863885718</v>
+      </c>
+      <c r="L18" t="n">
+        <v>698.3590313886807</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1485.137489129835</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.9988822303044389</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.9988826289648294</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>500</v>
+      </c>
+      <c r="B19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.0001231147864098138</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0001150312817627645</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.0001098005132761358</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.027849747003606e-05</v>
+      </c>
+      <c r="O19" t="n">
+        <v>8.213114728138009e-05</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>500</v>
+      </c>
+      <c r="B20" t="n">
+        <v>500</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>8.786649864547207e-06</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5.282590080723728e-06</v>
+      </c>
+      <c r="M20" t="n">
+        <v>9.17366559715932e-06</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.430033557997225e-05</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.840305174620177e-05</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>500</v>
+      </c>
+      <c r="B21" t="n">
+        <v>500</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.548075400513843e-06</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3.793946258528714e-06</v>
+      </c>
+      <c r="M21" t="n">
+        <v>5.664499765644322e-06</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8.168635047016511e-06</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.058303157044276e-05</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>500</v>
+      </c>
+      <c r="B22" t="n">
+        <v>500</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.988329435767237e-06</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5.311566104805357e-06</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5.416420598286436e-06</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.610566224304919e-06</v>
+      </c>
+      <c r="O22" t="n">
+        <v>5.866735593504934e-06</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>500</v>
+      </c>
+      <c r="B23" t="n">
+        <v>500</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.463399182462626e-07</v>
+      </c>
+      <c r="L23" t="n">
+        <v>3.737447598599238e-07</v>
+      </c>
+      <c r="M23" t="n">
+        <v>8.892137433593136e-07</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.419153540913675e-06</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.931673433439641e-06</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>500</v>
+      </c>
+      <c r="B24" t="n">
+        <v>500</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.658255192460437e-05</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.492225656533285e-05</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.472637741321506e-05</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.083270754859958e-05</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.380696307027369e-05</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>500</v>
+      </c>
+      <c r="B25" t="n">
+        <v>500</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>12</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.609654845777186e-05</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4.206944437806818e-05</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4.071655387954655e-05</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.706806439159727e-05</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.393920223313786e-05</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>500</v>
+      </c>
+      <c r="B26" t="n">
+        <v>500</v>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.0001657924076004045</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0001533340050531499</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.0001468521568645039</v>
+      </c>
+      <c r="N26" t="n">
+        <v>8.78510205602725e-05</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.0001130175922245447</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>500</v>
+      </c>
+      <c r="B27" t="n">
+        <v>500</v>
+      </c>
+      <c r="C27" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>12</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.001112175400725192</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.001040995413128885</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.0009934489969662581</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.0005364260902599588</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.0007408524652366573</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>500</v>
+      </c>
+      <c r="B28" t="n">
+        <v>500</v>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>12</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.003844730649185816</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.00359989670851326</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.003435127559833904</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.001844648901734966</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.002552827842982799</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>500</v>
+      </c>
+      <c r="B29" t="n">
+        <v>500</v>
+      </c>
+      <c r="C29" t="n">
+        <v>15</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>12</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.02108688636651432</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.01963672496993394</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.01874221505450752</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.01039066645838637</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.01373704241515422</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>500</v>
+      </c>
+      <c r="B30" t="n">
+        <v>500</v>
+      </c>
+      <c r="C30" t="n">
+        <v>20</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>12</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.0712046902970529</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.06620897944317371</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.06319961030921985</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.03403744889208701</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.04434371288840832</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>500</v>
+      </c>
+      <c r="B31" t="n">
+        <v>500</v>
+      </c>
+      <c r="C31" t="n">
+        <v>30</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>12</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.5034324192664091</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.4687789433200523</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.4474266713697132</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.1766429387716764</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.2278190013729098</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
         <v>30</v>
       </c>
     </row>

--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1166,4 +1167,930 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4212.326877272338</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2795.779531038314</v>
+      </c>
+      <c r="M2" t="n">
+        <v>5942.355564831777</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.9997205575778536</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.9997205824732387</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1052.19863885718</v>
+      </c>
+      <c r="L3" t="n">
+        <v>698.3590313886807</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1485.137489129835</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.9988822303044389</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.9988826289648294</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001231147864098138</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0001150312817627645</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0001098005132761358</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6.027849747003606e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>8.213114728138009e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8.786649864547207e-06</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.282590080723728e-06</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9.17366559715932e-06</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.430033557997225e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.840305174620177e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.548075400513843e-06</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.793946258528714e-06</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5.664499765644322e-06</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8.168635047016511e-06</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.058303157044276e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.988329435767237e-06</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5.311566104805357e-06</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5.416420598286436e-06</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.610566224304919e-06</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5.866735593504934e-06</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.463399182462626e-07</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.737447598599238e-07</v>
+      </c>
+      <c r="M8" t="n">
+        <v>8.892137433593136e-07</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.419153540913675e-06</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.931673433439641e-06</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.658255192460437e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.492225656533285e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.472637741321506e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.083270754859958e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.380696307027369e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.609654845777186e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.206944437806818e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4.071655387954655e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.706806439159727e-05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.393920223313786e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0001657924076004045</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0001533340050531499</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0001468521568645039</v>
+      </c>
+      <c r="N11" t="n">
+        <v>8.78510205602725e-05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0001130175922245447</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>500</v>
+      </c>
+      <c r="B12" t="n">
+        <v>500</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.001112175400725192</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.001040995413128885</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0009934489969662581</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0005364260902599588</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0007408524652366573</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>500</v>
+      </c>
+      <c r="B13" t="n">
+        <v>500</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.003844730649185816</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.00359989670851326</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.003435127559833904</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.001844648901734966</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.002552827842982799</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>500</v>
+      </c>
+      <c r="B14" t="n">
+        <v>500</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.02108688636651432</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.01963672496993394</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.01874221505450752</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.01039066645838637</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.01373704241515422</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>500</v>
+      </c>
+      <c r="B15" t="n">
+        <v>500</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0712046902970529</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.06620897944317371</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.06319961030921985</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.03403744889208701</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.04434371288840832</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>500</v>
+      </c>
+      <c r="B16" t="n">
+        <v>500</v>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.5034324192664091</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4687789433200523</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.4474266713697132</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.1766429387716764</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.2278190013729098</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2093,4 +2094,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.609654845777186e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4.206944437806818e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.071655387954655e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.706806439159727e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.393920223313786e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.609348972210357e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.20244902092943e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4.067383419948427e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.708838498630114e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.390857412148268e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001379502844955465</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0001248794063013906</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0001199491559447728</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8.359053703465446e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>9.354792148455726e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.000923923078716667</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0006393202384833579</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.001159601299885082</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0001213605306384066</v>
+      </c>
+      <c r="O5" t="n">
+        <v>9.358680687570199e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0008338776348568979</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0003022998471079869</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0008949708132870029</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0001892809369896124</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0001159246642778869</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0004988519043554852</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0003235170428686435</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.001284452433093799</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0004407398044087191</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.000250044096819048</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2652027144270129</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0870105890753466</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.3082353194815523</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0009034771038193271</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0001873865691055213</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01530357864426378</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.006615000738164614</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.01929059670996624</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.000296271738158157</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0002636238326762704</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.003027591777554353</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0008481740836390906</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.003555702481877079</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0002923296960054455</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0002938786562625513</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2690,4 +2691,655 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.609654845777186e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4.206944437806818e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.071655387954655e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.706806439159727e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.393920223313786e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.599218272403875e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.197058539454797e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4.062424003026023e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.702297498694041e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.388172418918662e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.612801614236616e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4.205739487585784e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4.07053947544666e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.712578306600843e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.393280218311805e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.609026083598802e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4.206271043541401e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.071025248162567e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.706479334084628e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.393519950484588e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.616641334651534e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.213464515760038e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4.077757336268891e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.709845121544952e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.397800066546544e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.615884791211162e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4.21271147665448e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4.077044557698268e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.709650465587808e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.397298813454464e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.614468757445482e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4.21135263474488e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4.07577819590496e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.709042468327624e-05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.396525570277329e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.611312510409451e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.208323249024204e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4.072946720492895e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.70761766102274e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.394746978472766e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.618372920430912e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.214235760855594e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4.078479018166372e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.710640323843887e-05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.398258249115474e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.624653288867456e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.21824180990263e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.082228276190436e-05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.713456409221407e-05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.400642156790028e-05</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3342,4 +3343,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.576761933824108e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.237642044688959e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.409574602867713e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.409745998719612e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.767639024169492e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7.880166260431448e-06</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6.247938084210613e-06</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.032736249811168e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.08416156125332e-05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.510125810069699e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.881658862023718e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.621013918266221e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.621013918242731e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.621051338967528e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.621040197109727e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.390194290367837e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.348119653737034e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.453624980663759e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.508110725362514e-05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.566520330447801e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.57510797096426e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.236294129989566e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.408584713060676e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.409374650515567e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.767235233306423e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.638142493173465e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.247601285332234e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.246846876054491e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.728493371875899e-05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.244430271570917e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.127592554424202e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.725234512054904e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.612455694953733e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.466493075905773e-05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.094950972381503e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.386094560065625e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.983518898080597e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.858130364636383e-05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.595426705775825e-05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.254320117577719e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.609654845777186e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.206944437806818e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4.071655387954655e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.706806439159727e-05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.393920223313786e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.638730486292129e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.23601121579278e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.099495856940188e-05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.721289394791384e-05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.412189995712641e-05</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>500</v>
+      </c>
+      <c r="B12" t="n">
+        <v>500</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.662179082599323e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4.259453993555728e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.121959400537129e-05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.732999116533698e-05</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.426942157545881e-05</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>500</v>
+      </c>
+      <c r="B13" t="n">
+        <v>500</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.665122169479711e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.262396302793927e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4.12477941318129e-05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.734468629519479e-05</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.428794747480844e-05</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>500</v>
+      </c>
+      <c r="B14" t="n">
+        <v>500</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.667479089083117e-05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4.264752581950763e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4.127037845743257e-05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.735645320295391e-05</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.430278528028381e-05</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Eigenvector Angle" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4159,4 +4160,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.612850401581469e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4.209888938415032e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.074416413072553e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.708326292826634e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.395707836928411e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.5786272492386125</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.4186901724508379</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.4934658077020039</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6167823814324462</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.5517564784290734</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.6378046824397647</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4827664611512805</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.4765776234148056</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5987023329804152</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.5122303711356031</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.5786272482732949</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4186901712992032</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.4934657509134684</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.6167823814329383</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.551756478436794</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.609654845777186e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.206944437806818e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4.071655387954655e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.706806439159727e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.393920223313786e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.5786272483506878</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.4186901712977214</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.4934657634341716</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.6167823814329014</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.5517564784280863</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.6378046824691279</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.4827664611365347</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.476577631565162</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5987023329804135</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5122303711296828</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.5786272495417162</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4186901724653425</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.4934658158714078</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.6167823814324791</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5517564784357842</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.612850401581469e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.209888938414877e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4.074416413072626e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.708326292826634e-05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.395707836928413e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2009,6 +2009,760 @@
         </is>
       </c>
       <c r="Q27" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>20</v>
+      </c>
+      <c r="B28" t="n">
+        <v>20</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.0002757210506970761</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.0001880308200762655</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.0004459234516276548</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.0007564967435892246</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.0009986075880267396</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>30</v>
+      </c>
+      <c r="B29" t="n">
+        <v>30</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>8.94130514132968e-05</v>
+      </c>
+      <c r="L29" t="n">
+        <v>7.653449593435425e-05</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.0002141802374216122</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.0003458890866205636</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.00048285207708024</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>50</v>
+      </c>
+      <c r="B30" t="n">
+        <v>50</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.314268206906132e-05</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2.922319519180245e-05</v>
+      </c>
+      <c r="M30" t="n">
+        <v>8.209189593442916e-05</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.0001308872308602571</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.00018349829092921</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>75</v>
+      </c>
+      <c r="B31" t="n">
+        <v>75</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.567137032342412e-05</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.348433417019511e-05</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.746133250560605e-05</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5.96816038439556e-05</v>
+      </c>
+      <c r="O31" t="n">
+        <v>8.338513803158042e-05</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>100</v>
+      </c>
+      <c r="B32" t="n">
+        <v>100</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>9.016506052198623e-06</v>
+      </c>
+      <c r="L32" t="n">
+        <v>7.711802166165057e-06</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2.131472441604473e-05</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.400878178126714e-05</v>
+      </c>
+      <c r="O32" t="n">
+        <v>4.736683263658282e-05</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125</v>
+      </c>
+      <c r="B33" t="n">
+        <v>125</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5.839171051862862e-06</v>
+      </c>
+      <c r="L33" t="n">
+        <v>4.97939486600134e-06</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.372705919210748e-05</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.187655074521899e-05</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.048099287508581e-05</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>150</v>
+      </c>
+      <c r="B34" t="n">
+        <v>150</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.079716615261009e-06</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3.476502909351208e-06</v>
+      </c>
+      <c r="M34" t="n">
+        <v>9.569975722855855e-06</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.525571617696953e-05</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.124086229863885e-05</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>175</v>
+      </c>
+      <c r="B35" t="n">
+        <v>175</v>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.011627808107967e-06</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2.563387142191317e-06</v>
+      </c>
+      <c r="M35" t="n">
+        <v>7.049844127937845e-06</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.123076415080959e-05</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.56430925351016e-05</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>200</v>
+      </c>
+      <c r="B36" t="n">
+        <v>200</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.316321522156805e-06</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.969452262858244e-06</v>
+      </c>
+      <c r="M36" t="n">
+        <v>5.408347539044994e-06</v>
+      </c>
+      <c r="N36" t="n">
+        <v>8.620772287592269e-06</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.199732063336666e-05</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>250</v>
+      </c>
+      <c r="B37" t="n">
+        <v>250</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.485364028350213e-06</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.263083642923515e-06</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.469708655526867e-06</v>
+      </c>
+      <c r="N37" t="n">
+        <v>5.529870103939049e-06</v>
+      </c>
+      <c r="O37" t="n">
+        <v>7.696213043069555e-06</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>300</v>
+      </c>
+      <c r="B38" t="n">
+        <v>300</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.053469384622325e-06</v>
+      </c>
+      <c r="L38" t="n">
+        <v>8.904466746138147e-07</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2.417146797857224e-06</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.85481675877871e-06</v>
+      </c>
+      <c r="O38" t="n">
+        <v>5.353295850368089e-06</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>500</v>
+      </c>
+      <c r="B39" t="n">
+        <v>500</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>5.405278515209248e-07</v>
+      </c>
+      <c r="L39" t="n">
+        <v>4.585782831118184e-07</v>
+      </c>
+      <c r="M39" t="n">
+        <v>9.153166916178774e-07</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.432082796546632e-06</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.916320927823261e-06</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>750</v>
+      </c>
+      <c r="B40" t="n">
+        <v>750</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.617664251642476e-06</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.461228202166996e-06</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.433405026894542e-06</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.027322427349149e-06</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.300340969999672e-06</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
         <v>750</v>
       </c>
     </row>
@@ -2023,7 +2777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2983,6 +3737,876 @@
         <v>30</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>500</v>
+      </c>
+      <c r="B17" t="n">
+        <v>500</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.189077298631476</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.160581100802471</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1605844947355088</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1913268879476932</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.1913268898834466</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>500</v>
+      </c>
+      <c r="B18" t="n">
+        <v>500</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.00384003804002427</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.003263143141915273</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.003261373352573354</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.003263970689560207</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.003263986328008423</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>500</v>
+      </c>
+      <c r="B19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.0005987073099629394</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0005517024852060242</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.000527172771209683</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.0003238776228220043</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.0003977430065033522</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>500</v>
+      </c>
+      <c r="B20" t="n">
+        <v>500</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.620856622086499e-05</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3.282832128427304e-05</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.20295649205397e-05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.235802993687709e-05</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.814093251340039e-05</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>500</v>
+      </c>
+      <c r="B21" t="n">
+        <v>500</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.222129181147043e-06</v>
+      </c>
+      <c r="L21" t="n">
+        <v>6.172274541716154e-06</v>
+      </c>
+      <c r="M21" t="n">
+        <v>7.289915288287353e-06</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8.731223118066459e-06</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.100465115521682e-05</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>500</v>
+      </c>
+      <c r="B22" t="n">
+        <v>500</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>7.167308709940751e-06</v>
+      </c>
+      <c r="L22" t="n">
+        <v>6.412464804707686e-06</v>
+      </c>
+      <c r="M22" t="n">
+        <v>6.400834121488268e-06</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.899426851071117e-06</v>
+      </c>
+      <c r="O22" t="n">
+        <v>6.348035241224952e-06</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>500</v>
+      </c>
+      <c r="B23" t="n">
+        <v>500</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5.405278515209248e-07</v>
+      </c>
+      <c r="L23" t="n">
+        <v>4.585782831118184e-07</v>
+      </c>
+      <c r="M23" t="n">
+        <v>9.153166916178774e-07</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.432082796546632e-06</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.916320927823261e-06</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>500</v>
+      </c>
+      <c r="B24" t="n">
+        <v>500</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.641902089292083e-05</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.476272832775284e-05</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.457989866150315e-05</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.076279005845392e-05</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.372369876824609e-05</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>500</v>
+      </c>
+      <c r="B25" t="n">
+        <v>500</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.613653546455149e-05</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4.210668610684143e-05</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4.075157505071832e-05</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.708524441250244e-05</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.396247415632201e-05</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>500</v>
+      </c>
+      <c r="B26" t="n">
+        <v>500</v>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.0001657852270685771</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0001533279243583069</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.0001468463622887232</v>
+      </c>
+      <c r="N26" t="n">
+        <v>8.784721126371284e-05</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.0001130133194943837</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>500</v>
+      </c>
+      <c r="B27" t="n">
+        <v>500</v>
+      </c>
+      <c r="C27" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.001112179461645204</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.001040999171856886</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.000993452573280729</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.0005364251495776959</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.0007408550578970063</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>500</v>
+      </c>
+      <c r="B28" t="n">
+        <v>500</v>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.00384459047541269</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.003599765924040152</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.003435002749569078</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.001844578153132325</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.002552735343720557</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>500</v>
+      </c>
+      <c r="B29" t="n">
+        <v>500</v>
+      </c>
+      <c r="C29" t="n">
+        <v>15</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.02108506722891057</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.01963503447649544</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.01874060134943081</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.01038976981330928</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.01373588097101363</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>500</v>
+      </c>
+      <c r="B30" t="n">
+        <v>500</v>
+      </c>
+      <c r="C30" t="n">
+        <v>20</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.07119336478287577</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.06619845522323374</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.0631895639553019</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.03403232083196017</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.04433709741652209</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>500</v>
+      </c>
+      <c r="B31" t="n">
+        <v>500</v>
+      </c>
+      <c r="C31" t="n">
+        <v>30</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.5031842322014282</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.4685473621227775</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.4472056680312433</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.1765833449404199</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.2277424738328437</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Results/rbf_fd_parameter_study_2.xlsx
+++ b/Results/rbf_fd_parameter_study_2.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2763,6 +2763,760 @@
         </is>
       </c>
       <c r="Q40" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>20</v>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.0002358360788938131</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.0001880308200762655</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.0004459234516276548</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.0007564967435892246</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.0009986075880267396</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>30</v>
+      </c>
+      <c r="B42" t="n">
+        <v>30</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="b">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>7.68543233689248e-05</v>
+      </c>
+      <c r="L42" t="n">
+        <v>7.653449593435425e-05</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.0002141802374216122</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.0003458890866205636</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.00048285207708024</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>50</v>
+      </c>
+      <c r="B43" t="n">
+        <v>50</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="b">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.822068617853745e-05</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2.922319519180245e-05</v>
+      </c>
+      <c r="M43" t="n">
+        <v>8.209189593442916e-05</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.0001308872308602571</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.00018349829092921</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>75</v>
+      </c>
+      <c r="B44" t="n">
+        <v>75</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="b">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1.3291742567397e-05</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.348433417019511e-05</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.746133250560605e-05</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5.96816038439556e-05</v>
+      </c>
+      <c r="O44" t="n">
+        <v>8.338513803158042e-05</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>100</v>
+      </c>
+      <c r="B45" t="n">
+        <v>100</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="b">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>7.658026210650555e-06</v>
+      </c>
+      <c r="L45" t="n">
+        <v>7.711802166165057e-06</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.131472441604473e-05</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.400878178126714e-05</v>
+      </c>
+      <c r="O45" t="n">
+        <v>4.736683263658282e-05</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125</v>
+      </c>
+      <c r="B46" t="n">
+        <v>125</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="b">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4.956295388826454e-06</v>
+      </c>
+      <c r="L46" t="n">
+        <v>4.97939486600134e-06</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.372705919210748e-05</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2.187655074521899e-05</v>
+      </c>
+      <c r="O46" t="n">
+        <v>3.048099287508581e-05</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>150</v>
+      </c>
+      <c r="B47" t="n">
+        <v>150</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="b">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.465682014775633e-06</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3.476502909351208e-06</v>
+      </c>
+      <c r="M47" t="n">
+        <v>9.569975722855855e-06</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1.525571617696953e-05</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2.124086229863885e-05</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>175</v>
+      </c>
+      <c r="B48" t="n">
+        <v>175</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="b">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.557408806440619e-06</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2.563387142191317e-06</v>
+      </c>
+      <c r="M48" t="n">
+        <v>7.049844127937845e-06</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1.123076415080959e-05</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1.56430925351016e-05</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>200</v>
+      </c>
+      <c r="B49" t="n">
+        <v>200</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="n">
+        <v>5</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="b">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1.967676710891083e-06</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1.969452262858244e-06</v>
+      </c>
+      <c r="M49" t="n">
+        <v>5.408347539044994e-06</v>
+      </c>
+      <c r="N49" t="n">
+        <v>8.620772287592269e-06</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.199732063336666e-05</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>250</v>
+      </c>
+      <c r="B50" t="n">
+        <v>250</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="n">
+        <v>5</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="b">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1.261715303731978e-06</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1.263083642923515e-06</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.469708655526867e-06</v>
+      </c>
+      <c r="N50" t="n">
+        <v>5.529870103939049e-06</v>
+      </c>
+      <c r="O50" t="n">
+        <v>7.696213043069555e-06</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>300</v>
+      </c>
+      <c r="B51" t="n">
+        <v>300</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="b">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>8.947931211680768e-07</v>
+      </c>
+      <c r="L51" t="n">
+        <v>8.904466746138147e-07</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2.417146797857224e-06</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3.85481675877871e-06</v>
+      </c>
+      <c r="O51" t="n">
+        <v>5.353295850368089e-06</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>500</v>
+      </c>
+      <c r="B52" t="n">
+        <v>500</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52" t="b">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>4.590735774498112e-07</v>
+      </c>
+      <c r="L52" t="n">
+        <v>4.585782831118184e-07</v>
+      </c>
+      <c r="M52" t="n">
+        <v>9.153166916178774e-07</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1.432082796546632e-06</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1.916320927823261e-06</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>750</v>
+      </c>
+      <c r="B53" t="n">
+        <v>750</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>5</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" t="b">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1.373849350562543e-06</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1.461228202166996e-06</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.433405026894542e-06</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1.027322427349149e-06</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1.300340969999672e-06</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>N_int</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
         <v>750</v>
       </c>
     </row>
@@ -2777,7 +3531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4607,6 +5361,876 @@
         <v>30</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>500</v>
+      </c>
+      <c r="B32" t="n">
+        <v>500</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.1605844946806367</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.160581100802471</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.1605844947355088</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.1913268879476932</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.1913268898834466</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>500</v>
+      </c>
+      <c r="B33" t="n">
+        <v>500</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.00326136756064837</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.003263143141915273</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.003261373352573354</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.003263970689560207</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.003263986328008423</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>500</v>
+      </c>
+      <c r="B34" t="n">
+        <v>500</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.0005084857438088917</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.0005517024852060242</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.000527172771209683</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.0003238776228220043</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.0003977430065033522</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>500</v>
+      </c>
+      <c r="B35" t="n">
+        <v>500</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.075215455146145e-05</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3.282832128427304e-05</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.20295649205397e-05</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.235802993687709e-05</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.814093251340039e-05</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>500</v>
+      </c>
+      <c r="B36" t="n">
+        <v>500</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>6.133798046973533e-06</v>
+      </c>
+      <c r="L36" t="n">
+        <v>6.172274541716154e-06</v>
+      </c>
+      <c r="M36" t="n">
+        <v>7.289915288287353e-06</v>
+      </c>
+      <c r="N36" t="n">
+        <v>8.731223118066459e-06</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.100465115521682e-05</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>500</v>
+      </c>
+      <c r="B37" t="n">
+        <v>500</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>6.087238688814016e-06</v>
+      </c>
+      <c r="L37" t="n">
+        <v>6.412464804707686e-06</v>
+      </c>
+      <c r="M37" t="n">
+        <v>6.400834121488268e-06</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4.899426851071117e-06</v>
+      </c>
+      <c r="O37" t="n">
+        <v>6.348035241224952e-06</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>500</v>
+      </c>
+      <c r="B38" t="n">
+        <v>500</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.590735774498112e-07</v>
+      </c>
+      <c r="L38" t="n">
+        <v>4.585782831118184e-07</v>
+      </c>
+      <c r="M38" t="n">
+        <v>9.153166916178774e-07</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.432082796546632e-06</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.916320927823261e-06</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>500</v>
+      </c>
+      <c r="B39" t="n">
+        <v>500</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.394477386933422e-05</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.476272832775284e-05</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.457989866150315e-05</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.076279005845392e-05</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.372369876824609e-05</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>500</v>
+      </c>
+      <c r="B40" t="n">
+        <v>500</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.918403894869758e-05</v>
+      </c>
+      <c r="L40" t="n">
+        <v>4.210668610684143e-05</v>
+      </c>
+      <c r="M40" t="n">
+        <v>4.075157505071832e-05</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.708524441250244e-05</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3.396247415632201e-05</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>500</v>
+      </c>
+      <c r="B41" t="n">
+        <v>500</v>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.0001408023972577012</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.0001533279243583069</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.0001468463622887232</v>
+      </c>
+      <c r="N41" t="n">
+        <v>8.784721126371284e-05</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.0001130133194943837</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>500</v>
+      </c>
+      <c r="B42" t="n">
+        <v>500</v>
+      </c>
+      <c r="C42" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="b">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.0009445807515506046</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.001040999171856886</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.000993452573280729</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.0005364251495776959</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.0007408550578970063</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>500</v>
+      </c>
+      <c r="B43" t="n">
+        <v>500</v>
+      </c>
+      <c r="C43" t="n">
+        <v>10</v>
+      </c>
+      <c r="D43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="b">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.003265233971590916</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.003599765924040152</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.003435002749569078</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.001844578153132325</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.002552735343720557</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>500</v>
+      </c>
+      <c r="B44" t="n">
+        <v>500</v>
+      </c>
+      <c r="C44" t="n">
+        <v>15</v>
+      </c>
+      <c r="D44" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="b">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.01790767527761895</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.01963503447649544</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.01874060134943081</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.01038976981330928</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.01373588097101363</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>500</v>
+      </c>
+      <c r="B45" t="n">
+        <v>500</v>
+      </c>
+      <c r="C45" t="n">
+        <v>20</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="b">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.06046495581976309</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.06619845522323374</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.0631895639553019</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.03403232083196017</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.04433709741652209</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>500</v>
+      </c>
+      <c r="B46" t="n">
+        <v>500</v>
+      </c>
+      <c r="C46" t="n">
+        <v>30</v>
+      </c>
+      <c r="D46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>lambda p: 1e0</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>lambda p: 1e-3</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>lambda p: 12.0/24.0*np.pi</t>
+        </is>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="b">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.4273574154283958</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.4685473621227775</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.4472056680312433</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.1765833449404199</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.2277424738328437</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
